--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122873205</v>
+        <v>122833916</v>
       </c>
       <c r="B2" t="n">
         <v>98355</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543765</v>
+        <v>543738</v>
       </c>
       <c r="R2" t="n">
-        <v>6711502</v>
+        <v>6711366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -914,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833683</v>
+        <v>122833965</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543720</v>
+        <v>543767</v>
       </c>
       <c r="R4" t="n">
-        <v>6711350</v>
+        <v>6711494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833814</v>
+        <v>122833683</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1075,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543735</v>
+        <v>543720</v>
       </c>
       <c r="R5" t="n">
-        <v>6711349</v>
+        <v>6711350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833965</v>
+        <v>122833814</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1192,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543767</v>
+        <v>543735</v>
       </c>
       <c r="R6" t="n">
-        <v>6711494</v>
+        <v>6711349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833916</v>
+        <v>122873068</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1309,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543738</v>
+        <v>543749</v>
       </c>
       <c r="R7" t="n">
-        <v>6711366</v>
+        <v>6711507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122873068</v>
+        <v>122873205</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543749</v>
+        <v>543765</v>
       </c>
       <c r="R8" t="n">
-        <v>6711507</v>
+        <v>6711502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122833916</v>
+        <v>122833683</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543738</v>
+        <v>543720</v>
       </c>
       <c r="R2" t="n">
-        <v>6711366</v>
+        <v>6711350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +795,7 @@
         <v>122833885</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833965</v>
+        <v>122833916</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543767</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6711494</v>
+        <v>6711366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833683</v>
+        <v>122873205</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543720</v>
+        <v>543765</v>
       </c>
       <c r="R5" t="n">
-        <v>6711350</v>
+        <v>6711502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833814</v>
+        <v>122833965</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543735</v>
+        <v>543767</v>
       </c>
       <c r="R6" t="n">
-        <v>6711349</v>
+        <v>6711494</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122873068</v>
+        <v>122833814</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543749</v>
+        <v>543735</v>
       </c>
       <c r="R7" t="n">
-        <v>6711507</v>
+        <v>6711349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122873205</v>
+        <v>122873068</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543765</v>
+        <v>543749</v>
       </c>
       <c r="R8" t="n">
-        <v>6711502</v>
+        <v>6711507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122833683</v>
+        <v>122873205</v>
       </c>
       <c r="B2" t="n">
         <v>98357</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543720</v>
+        <v>543765</v>
       </c>
       <c r="R2" t="n">
-        <v>6711350</v>
+        <v>6711502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122833885</v>
+        <v>122873068</v>
       </c>
       <c r="B3" t="n">
         <v>98357</v>
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543736</v>
+        <v>543749</v>
       </c>
       <c r="R3" t="n">
-        <v>6711368</v>
+        <v>6711507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833916</v>
+        <v>122833885</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -953,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543736</v>
       </c>
       <c r="R4" t="n">
-        <v>6711366</v>
+        <v>6711368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122873205</v>
+        <v>122833916</v>
       </c>
       <c r="B5" t="n">
         <v>98357</v>
@@ -1070,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543765</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6711502</v>
+        <v>6711366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833965</v>
+        <v>122833683</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1192,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543767</v>
+        <v>543720</v>
       </c>
       <c r="R6" t="n">
-        <v>6711494</v>
+        <v>6711350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833814</v>
+        <v>122833965</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1309,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543735</v>
+        <v>543767</v>
       </c>
       <c r="R7" t="n">
-        <v>6711349</v>
+        <v>6711494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122873068</v>
+        <v>122833814</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1426,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543749</v>
+        <v>543735</v>
       </c>
       <c r="R8" t="n">
-        <v>6711507</v>
+        <v>6711349</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122873205</v>
+        <v>122873068</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543765</v>
+        <v>543749</v>
       </c>
       <c r="R2" t="n">
-        <v>6711502</v>
+        <v>6711507</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122873068</v>
+        <v>122833683</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543749</v>
+        <v>543720</v>
       </c>
       <c r="R3" t="n">
-        <v>6711507</v>
+        <v>6711350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833885</v>
+        <v>122833814</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543736</v>
+        <v>543735</v>
       </c>
       <c r="R4" t="n">
-        <v>6711368</v>
+        <v>6711349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833916</v>
+        <v>122833885</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>543736</v>
       </c>
       <c r="R5" t="n">
-        <v>6711366</v>
+        <v>6711368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833683</v>
+        <v>122833916</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543720</v>
+        <v>543738</v>
       </c>
       <c r="R6" t="n">
-        <v>6711350</v>
+        <v>6711366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,7 +1268,7 @@
         <v>122833965</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1387,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122833814</v>
+        <v>122873205</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543735</v>
+        <v>543765</v>
       </c>
       <c r="R8" t="n">
-        <v>6711349</v>
+        <v>6711502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122873068</v>
+        <v>122833683</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543749</v>
+        <v>543720</v>
       </c>
       <c r="R2" t="n">
-        <v>6711507</v>
+        <v>6711350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122833683</v>
+        <v>122873068</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543720</v>
+        <v>543749</v>
       </c>
       <c r="R3" t="n">
-        <v>6711350</v>
+        <v>6711507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122833683</v>
+        <v>122833965</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543720</v>
+        <v>543767</v>
       </c>
       <c r="R2" t="n">
-        <v>6711350</v>
+        <v>6711494</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122873068</v>
+        <v>122833814</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543749</v>
+        <v>543735</v>
       </c>
       <c r="R3" t="n">
-        <v>6711507</v>
+        <v>6711349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833814</v>
+        <v>122873068</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543735</v>
+        <v>543749</v>
       </c>
       <c r="R4" t="n">
-        <v>6711349</v>
+        <v>6711507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1148,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833916</v>
+        <v>122833683</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543738</v>
+        <v>543720</v>
       </c>
       <c r="R6" t="n">
-        <v>6711366</v>
+        <v>6711350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833965</v>
+        <v>122873205</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543767</v>
+        <v>543765</v>
       </c>
       <c r="R7" t="n">
-        <v>6711494</v>
+        <v>6711502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122873205</v>
+        <v>122833916</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1426,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543765</v>
+        <v>543738</v>
       </c>
       <c r="R8" t="n">
-        <v>6711502</v>
+        <v>6711366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122833965</v>
+        <v>122833683</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543767</v>
+        <v>543720</v>
       </c>
       <c r="R2" t="n">
-        <v>6711494</v>
+        <v>6711350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122833814</v>
+        <v>122833916</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543735</v>
+        <v>543738</v>
       </c>
       <c r="R3" t="n">
-        <v>6711349</v>
+        <v>6711366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122873068</v>
+        <v>122873205</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543749</v>
+        <v>543765</v>
       </c>
       <c r="R4" t="n">
-        <v>6711507</v>
+        <v>6711502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833885</v>
+        <v>122873068</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543736</v>
+        <v>543749</v>
       </c>
       <c r="R5" t="n">
-        <v>6711368</v>
+        <v>6711507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833683</v>
+        <v>122833814</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1192,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543720</v>
+        <v>543735</v>
       </c>
       <c r="R6" t="n">
-        <v>6711350</v>
+        <v>6711349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122873205</v>
+        <v>122833885</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1309,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543765</v>
+        <v>543736</v>
       </c>
       <c r="R7" t="n">
-        <v>6711502</v>
+        <v>6711368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122833916</v>
+        <v>122833965</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543738</v>
+        <v>543767</v>
       </c>
       <c r="R8" t="n">
-        <v>6711366</v>
+        <v>6711494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122833683</v>
+        <v>122873205</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543720</v>
+        <v>543765</v>
       </c>
       <c r="R2" t="n">
-        <v>6711350</v>
+        <v>6711502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122833916</v>
+        <v>122833683</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543738</v>
+        <v>543720</v>
       </c>
       <c r="R3" t="n">
-        <v>6711366</v>
+        <v>6711350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122873205</v>
+        <v>122833916</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -953,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543765</v>
+        <v>543738</v>
       </c>
       <c r="R4" t="n">
-        <v>6711502</v>
+        <v>6711366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122873068</v>
+        <v>122833965</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543749</v>
+        <v>543767</v>
       </c>
       <c r="R5" t="n">
-        <v>6711507</v>
+        <v>6711494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833814</v>
+        <v>122833885</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1197,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543735</v>
+        <v>543736</v>
       </c>
       <c r="R6" t="n">
-        <v>6711349</v>
+        <v>6711368</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833885</v>
+        <v>122833814</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1314,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543736</v>
+        <v>543735</v>
       </c>
       <c r="R7" t="n">
-        <v>6711368</v>
+        <v>6711349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122833965</v>
+        <v>122873068</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1431,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543767</v>
+        <v>543749</v>
       </c>
       <c r="R8" t="n">
-        <v>6711494</v>
+        <v>6711507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122873205</v>
+        <v>122873068</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543765</v>
+        <v>543749</v>
       </c>
       <c r="R2" t="n">
-        <v>6711502</v>
+        <v>6711507</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122833683</v>
+        <v>122833916</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543720</v>
+        <v>543738</v>
       </c>
       <c r="R3" t="n">
-        <v>6711350</v>
+        <v>6711366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833916</v>
+        <v>122833814</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543738</v>
+        <v>543735</v>
       </c>
       <c r="R4" t="n">
-        <v>6711366</v>
+        <v>6711349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833965</v>
+        <v>122833683</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543767</v>
+        <v>543720</v>
       </c>
       <c r="R5" t="n">
-        <v>6711494</v>
+        <v>6711350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833885</v>
+        <v>122873205</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543736</v>
+        <v>543765</v>
       </c>
       <c r="R6" t="n">
-        <v>6711368</v>
+        <v>6711502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833814</v>
+        <v>122833885</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543735</v>
+        <v>543736</v>
       </c>
       <c r="R7" t="n">
-        <v>6711349</v>
+        <v>6711368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122873068</v>
+        <v>122833965</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543749</v>
+        <v>543767</v>
       </c>
       <c r="R8" t="n">
-        <v>6711507</v>
+        <v>6711494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122873068</v>
+        <v>122833814</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543749</v>
+        <v>543735</v>
       </c>
       <c r="R2" t="n">
-        <v>6711507</v>
+        <v>6711349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bladrosetter på en yta av cirka 2m2.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122833916</v>
+        <v>122873205</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543738</v>
+        <v>543765</v>
       </c>
       <c r="R3" t="n">
-        <v>6711366</v>
+        <v>6711502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833814</v>
+        <v>122833885</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543735</v>
+        <v>543736</v>
       </c>
       <c r="R4" t="n">
-        <v>6711349</v>
+        <v>6711368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833683</v>
+        <v>122833916</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543720</v>
+        <v>543738</v>
       </c>
       <c r="R5" t="n">
-        <v>6711350</v>
+        <v>6711366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122873205</v>
+        <v>122833683</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543765</v>
+        <v>543720</v>
       </c>
       <c r="R6" t="n">
-        <v>6711502</v>
+        <v>6711350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833885</v>
+        <v>122833965</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543736</v>
+        <v>543767</v>
       </c>
       <c r="R7" t="n">
-        <v>6711368</v>
+        <v>6711494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122833965</v>
+        <v>122873068</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543767</v>
+        <v>543749</v>
       </c>
       <c r="R8" t="n">
-        <v>6711494</v>
+        <v>6711507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bladrosetter på en yta av cirka 2m2.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54330-2024 artfynd.xlsx
+++ b/artfynd/A 54330-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122833814</v>
+        <v>122833916</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543735</v>
+        <v>543738</v>
       </c>
       <c r="R2" t="n">
-        <v>6711349</v>
+        <v>6711366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122873205</v>
+        <v>122833814</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543765</v>
+        <v>543735</v>
       </c>
       <c r="R3" t="n">
-        <v>6711502</v>
+        <v>6711349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833885</v>
+        <v>122873205</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543736</v>
+        <v>543765</v>
       </c>
       <c r="R4" t="n">
-        <v>6711368</v>
+        <v>6711502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda på en yta av cirka 1m2.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833916</v>
+        <v>122833965</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543738</v>
+        <v>543767</v>
       </c>
       <c r="R5" t="n">
-        <v>6711366</v>
+        <v>6711494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1151,7 @@
         <v>122833683</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122833965</v>
+        <v>122833885</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543767</v>
+        <v>543736</v>
       </c>
       <c r="R7" t="n">
-        <v>6711494</v>
+        <v>6711368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1385,7 @@
         <v>122873068</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
